--- a/backend/data/financials_by_company/12J0.F.xlsx
+++ b/backend/data/financials_by_company/12J0.F.xlsx
@@ -4256,10 +4256,8 @@
           <t>Toulouse</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>31079</t>
-        </is>
+      <c r="D2" t="n">
+        <v>31079</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -4456,7 +4454,7 @@
         <v>-32141000</v>
       </c>
       <c r="BI2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
@@ -4684,7 +4682,7 @@
         <v>0</v>
       </c>
       <c r="DS2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DT2" t="n">
         <v>-0.0026699994</v>
